--- a/data/Nick_Stock_Desk_Starter.xlsx
+++ b/data/Nick_Stock_Desk_Starter.xlsx
@@ -469,8 +469,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="88" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -489,7 +493,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Each tab loads one CSV with IMPORTDATA. After you upload the file to Google Sheets, use Extensions &gt; Apps Script and paste apps_script/Refresh.gs so the Desk menu can reload them.</t>
+          <t>These tabs only have headers. After you open this file in Google Sheets, paste apps_script/Refresh.gs and use Desk &gt; Refresh data now. The script copies each file into the tab with the same name. Do not use IMPORTDATA.</t>
         </is>
       </c>
     </row>
@@ -505,10 +509,23 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>If a tab says the resource was not found, the files are not on the main branch yet. Wait until the pull request is merged.</t>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Last refresh</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Not loaded yet. Use Desk &gt; Refresh data now.</t>
         </is>
       </c>
     </row>
@@ -523,13 +540,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/portfolio_summary.csv")</f>
-        <v/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>day_pnl</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>day_pnl_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>total_gain</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>total_gain_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>needs_attention</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>n_holdings</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>example_warning</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -543,13 +616,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/watchlist.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>distance_to_entry_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note_input</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -563,13 +702,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/prices.csv")</f>
-        <v/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>close</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sma20</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sma50</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>trade_target</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -583,13 +763,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/news.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -603,13 +829,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_growth.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rev_growth</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rs_spy_3m</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -623,13 +915,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_quality.csv")</f>
-        <v/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>roe</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_roe</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pts_de</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -643,13 +1006,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_dividend.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>div_yield</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>div_yield_avg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_div_yield</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -663,13 +1092,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_wheel.csv")</f>
-        <v/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rsi14</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>dollar_volume</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -683,13 +1183,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_vcp.csv")</f>
-        <v/>
+  <dimension ref="A1:AE1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pivot</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>trail</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>trend_score</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>contractions</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>depths</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>volume_ok</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>in_trade</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>stop_basis</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>r1</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>r2</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>r3</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>r4</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>r5</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>r6</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>r7</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>r8</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -703,13 +1354,179 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_canslim.csv")</f>
-        <v/>
+  <dimension ref="A1:AH1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pivot</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>c_quarterly_eps</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>c_status</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>a_annual_eps</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>a_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>n_pct_from_high</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>n_status</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>s_adv</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>s_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>l_rs_percentile</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>l_status</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>i_trend</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>i_status</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>m_market</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>m_spy</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>m_qqq</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>m_status</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>qualify</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>vcp_heuristic</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -723,13 +1540,539 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scores.csv")</f>
-        <v/>
+  <dimension ref="A1:DB1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>universe</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pts_tech</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pts_fin</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pts_sent</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>pts_earnings</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>pts_sector</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>pts_trend</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pts_oscillator</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>pts_forward_pe</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>pts_ttm_pe</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pts_ps</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pts_de</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>pts_pfcf</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pts_rev_growth</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pts_eps_growth</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pts_roe</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pts_div_yield</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pts_analyst</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>pts_institutional</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>pts_insider</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>forward_pe</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>forward_pe_avg</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ttm_pe</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>ttm_pe_avg</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>ps</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>ps_avg</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>de_avg</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>pfcf</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>pfcf_avg</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>rev_growth</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>rev_growth_avg</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>eps_growth</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>eps_growth_avg</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>roe</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>roe_avg</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>div_yield</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>div_yield_avg</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>forward_pe_avg_basis</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>fin_avg_years</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>fundamentals_basis</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>fundamentals_filed</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>ind_forward_pe</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>pts_forward_pe_ind</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>ind_ttm_pe</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>pts_ttm_pe_ind</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>ind_ps</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>pts_ps_ind</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>ind_de</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>pts_de_ind</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>ind_pfcf</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>pts_pfcf_ind</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>ind_rev_growth</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>pts_rev_growth_ind</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>ind_eps_growth</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>pts_eps_growth_ind</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>ind_roe</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>pts_roe_ind</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>ind_div_yield</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>pts_div_yield_ind</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>analyst_mean</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>analyst_count</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>target_analyst</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>target_analyst_kind</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>target_pfcf</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>target_peg</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>target_blended</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>target_blend_n</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>trade_target</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>reward_risk</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>timing</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>sma_alignment</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>rsi14</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>rs_spy_3m</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>dist_52w_high_pct</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>next_earnings</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>missing_fields</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>missing_count</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>price_status</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>fundamentals_status</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>analyst_status</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>holders_status</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -743,13 +2086,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_box.csv")</f>
-        <v/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pivot</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>range_days</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>range_width_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -763,13 +2197,109 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_flag.csv")</f>
-        <v/>
+  <dimension ref="A1:T1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pivot</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pole_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>flag_bars</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>retrace_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -783,13 +2313,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/scanner_leaders.csv")</f>
-        <v/>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pivot</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>freshness</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>vcp_status</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>canslim_status</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>vcp_strength</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>canslim_strength</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>on_vcp</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>on_canslim</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -803,13 +2439,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/earnings_calendar.csv")</f>
-        <v/>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>next_earnings</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>when_hint</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>days_away</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>last_eps_actual</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>last_eps_estimate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>last_surprise_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>last_1d_move_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>avg_1d_move_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>n_past</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>owns</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -823,13 +2530,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/earnings_heatmap.csv")</f>
-        <v/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>quarter</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps_flag</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>rev_flag</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>heat</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -843,13 +2591,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/earnings_cards.csv")</f>
-        <v/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>grade</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>summary</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -863,13 +2647,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/earnings_history.csv")</f>
-        <v/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>earnings_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps_estimate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>eps_actual</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>surprise_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>move_1d_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -883,13 +2708,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/put_call.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ma5</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fear_line</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>greed_line</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -903,13 +2774,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/option_walls.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>strike</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>open_interest</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_wall</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -923,13 +2840,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/analyst_ratings.csv")</f>
-        <v/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>analyst_mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>analyst_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pts_analyst</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>target_analyst</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>target_analyst_kind</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upside_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -943,13 +2916,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/score_details.csv")</f>
-        <v/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>points_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>now_value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>vs_industry</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -963,13 +2972,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/institutional_13f.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>increased_shares</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>decreased_shares</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>holders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ownership_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>share_change</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pts_institutional</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -983,13 +3058,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/aaii_sentiment.csv")</f>
-        <v/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bullish_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>neutral_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bearish_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1003,13 +3109,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/insider_trading.csv")</f>
-        <v/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>buys_3m</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sells_3m</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pts_insider</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1023,13 +3160,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/headline_sentiment.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tone</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tone_note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1043,13 +3226,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/xly_xlp.csv")</f>
-        <v/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>xly</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>xlp</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ratio_sma50</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1063,13 +3287,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/financials_summary.csv")</f>
-        <v/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>now_value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_3y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pts_vs_self</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>industry_median</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_vs_industry</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1083,13 +3363,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/earnings_tracker.csv")</f>
-        <v/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>earnings_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps_estimate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>eps_actual</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>surprise_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1103,13 +3424,99 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/company_financials.csv")</f>
-        <v/>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fy_end</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>filed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>gross_profit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>op_income</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>operating_margin</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_margin</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>fcf</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ps</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pfcf</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1123,13 +3530,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/dividend_scanner.csv")</f>
-        <v/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>div_yield</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>div_yield_avg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pts_div_yield</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1143,13 +3606,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/macro_screener.csv")</f>
-        <v/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>forecast</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>surprise</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1163,13 +3677,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/market_today.csv")</f>
-        <v/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>spy_price</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>spy_day_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>breadth_sma20</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>breadth_sma50</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>breadth_sma100</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>breadth_sma200</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>breadth_sma50_week_ago</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>advancers</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>decliners</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>universe_n</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>highs_52w</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>lows_52w</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>put_call</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>put_call_ma5</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>put_call_zone</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>put_call_name</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>fred_dgs10</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>fred_t10y2y</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>xly_xlp</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>updated_pt</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1183,13 +3818,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/sector_macro.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>macro_growth</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>macro_inflation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>macro_jobs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>macro_score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>plain_english</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1203,13 +3884,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/historical_pe.csv")</f>
-        <v/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>desk_median_trailing_pe</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>official_sp500_pe</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>official_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1223,13 +3940,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/breakouts.csv")</f>
-        <v/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dist_52w_high_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1243,13 +4011,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/trends.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>trend_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sma_alignment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1263,13 +4097,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/pullbacks.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rsi14</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1283,13 +4183,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/gainers_losers.csv")</f>
-        <v/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1303,13 +4254,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/sector_performance.csv")</f>
-        <v/>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>month_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>month3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ytd_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>score_avg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1323,13 +4330,79 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/heatmaps.csv")</f>
-        <v/>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ret_1d</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ret_1w</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ret_1m</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ret_ytd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1343,13 +4416,39 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/freshness.csv")</f>
-        <v/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_missing</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_present</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1363,13 +4462,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/updates_log.csv")</f>
-        <v/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>checked_pt</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1383,13 +4503,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/sectors.csv")</f>
-        <v/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>week_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>month_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>month3_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ytd_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rs_3m_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>score_avg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>n_stocks</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>macro_growth</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_inflation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>macro_jobs</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>macro_score</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1403,13 +4614,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/help.csv")</f>
-        <v/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plain_english</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1423,13 +4640,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/settings.csv")</f>
-        <v/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1443,13 +4666,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/universe.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>in_sp500</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>in_ndx100</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>in_growth</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1463,13 +4732,104 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/backtest_summary.csv")</f>
-        <v/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top20_cagr_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>spy_cagr_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bottom20_cagr_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>top20_total_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>spy_total_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>bottom20_total_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top20_max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spy_max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>hit_rate_12w_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>top_bucket_excess_12w_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>is_headline</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1483,13 +4843,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/backtest_buckets.csv")</f>
-        <v/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_return_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_spy_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>excess_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>hit_rate_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1503,13 +4909,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/backtest_equity.csv")</f>
-        <v/>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>top20</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spy</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bottom20</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1523,13 +4960,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/backtest_yearly.csv")</f>
-        <v/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>top20_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spy_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>difference_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hit_rate_12w_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>signals</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1543,13 +5021,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/backtest_notes.csv")</f>
-        <v/>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1563,13 +5062,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/breadth_history.csv")</f>
-        <v/>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pct_above_sma20</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_above_sma100</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_above_sma200</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1583,13 +5118,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/alerts.csv")</f>
-        <v/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score_prev</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verdict_prev</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1603,13 +5189,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/score_changes.csv")</f>
-        <v/>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>score_prev</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_change</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1623,13 +5260,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1">
-        <f>IMPORTDATA("https://raw.githubusercontent.com/PatelNicknp/nicks-stock-desk/main/data/portfolio.csv")</f>
-        <v/>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_cost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gain</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gain_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>weight_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>score_week_ago</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>score_week_change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/Nick_Stock_Desk_Starter.xlsx
+++ b/data/Nick_Stock_Desk_Starter.xlsx
@@ -3677,7 +3677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3693,116 +3693,1689 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>qqq_day_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>buy_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>breadth_sma20</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>breadth_sma50</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>breadth_sma100</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>breadth_sma200</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>breadth_sma50_week_ago</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>advancers</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>decliners</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>universe_n</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>highs_52w</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lows_52w</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>put_call</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>put_call_ma5</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>put_call_zone</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>put_call_name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fred_dgs10</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fred_t10y2y</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>xly_xlp</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>updated_pt</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>macro_growth</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>breadth_sma50</t>
+          <t>macro_inflation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>breadth_sma100</t>
+          <t>macro_jobs</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>breadth_sma200</t>
+          <t>macro_score</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>breadth_sma50_week_ago</t>
+          <t>plain_english</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>advancers</t>
+          <t>data_status</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>decliners</t>
+          <t>note</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>universe_n</t>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>desk_median_trailing_pe</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>official_sp500_pe</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>official_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dist_52w_high_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>highs_52w</t>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>trend_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sma_alignment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>score</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>lows_52w</t>
+          <t>data_status</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>put_call</t>
+          <t>note</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>put_call_ma5</t>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rsi14</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>month_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>month3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ytd_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>score_avg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ret_1d</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ret_1w</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ret_1m</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ret_ytd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_missing</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_present</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>checked_pt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>week_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>month_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>month3_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ytd_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rs_3m_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>score_avg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>n_stocks</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>macro_growth</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_inflation</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>put_call_zone</t>
+          <t>macro_jobs</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>put_call_name</t>
+          <t>macro_score</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>vix</t>
+          <t>data_status</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>fred_dgs10</t>
+          <t>note</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>fred_t10y2y</t>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plain_english</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>index_membership</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>in_sp500</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>in_ndx100</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>in_growth</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top20_cagr_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>spy_cagr_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bottom20_cagr_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>top20_total_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>spy_total_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>bottom20_total_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top20_max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spy_max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>hit_rate_12w_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>top_bucket_excess_12w_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>is_headline</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_return_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_spy_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>excess_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>hit_rate_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>top20</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spy</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bottom20</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>top20_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spy_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>difference_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hit_rate_12w_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>signals</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pct_above_sma20</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_above_sma100</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_above_sma200</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score_prev</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verdict_prev</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>score_prev</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_change</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_cost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gain</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gain_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>weight_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>score_week_ago</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>score_week_change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>data_status</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>xly_xlp</t>
+          <t>note</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>updated_pt</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>price_as_of</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
           <t>disclaimer</t>
         </is>
       </c>
@@ -3810,1567 +5383,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>macro_growth</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>macro_inflation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>macro_jobs</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>macro_score</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>plain_english</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>desk_median_trailing_pe</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>official_sp500_pe</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>official_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>dist_52w_high_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>volume_ratio</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>trend_label</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>sma_alignment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>above_sma20</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>above_sma50</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>above_sma100</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>above_sma200</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rsi14</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>entry_low</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>entry_high</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>passes</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>why</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>side</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>month_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>month3_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ytd_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pct_above_sma50</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>score_avg</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ret_1d</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ret_1w</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ret_1m</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ret_ytd</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>above_sma20</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>above_sma50</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>above_sma100</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>above_sma200</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>n_missing</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n_present</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>checked_pt</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>group_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>week_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>month_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>month3_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ytd_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>rs_3m_pct</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>score_avg</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>n_stocks</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pct_above_sma50</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>macro_growth</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>macro_inflation</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>macro_jobs</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>macro_score</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>topic</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>plain_english</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>setting</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>index_membership</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>in_sp500</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>in_ndx100</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>in_growth</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>top20_cagr_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>spy_cagr_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bottom20_cagr_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>top20_total_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>spy_total_pct</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>bottom20_total_pct</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>top20_max_drawdown_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>spy_max_drawdown_pct</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>hit_rate_12w_pct</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>top_bucket_excess_12w_pct</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>headline</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>is_headline</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>horizon</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>bucket</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>avg_return_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>avg_spy_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>excess_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>hit_rate_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>top20</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bottom20</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>top20_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spy_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>difference_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>hit_rate_12w_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>signals</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pct_above_sma20</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>pct_above_sma50</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pct_above_sma100</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>pct_above_sma200</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>score_prev</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>verdict_prev</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>score_prev</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score_change</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>shares</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>avg_cost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>gain</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>gain_pct</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>weight_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>score_week_ago</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>score_week_change</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/data/Nick_Stock_Desk_Starter.xlsx
+++ b/data/Nick_Stock_Desk_Starter.xlsx
@@ -2774,6 +2774,397 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>strike</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>open_interest</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_wall</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>nearest_expiry</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>analyst_mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>analyst_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pts_analyst</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>target_analyst</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>target_analyst_kind</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>upside_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>points</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>points_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>now_value</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>avg_value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>vs_industry</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>row_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>increased_shares</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>decreased_shares</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>holders</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ownership_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>share_change</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pts_institutional</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>as_of</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bullish_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>neutral_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bearish_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>buys_3m</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sells_3m</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pts_insider</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2785,46 +3176,1246 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>expiry</t>
+          <t>headline</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>publisher</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>published</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>tone</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tone_note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>xly</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>xlp</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ratio_sma50</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>now_value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_3y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pts_vs_self</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>industry_median</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_vs_industry</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>earnings_date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps_estimate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>eps_actual</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>surprise_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fy_end</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>filed</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>gross_profit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>op_income</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>operating_margin</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>net_margin</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>fcf</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>pe</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ps</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pfcf</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>div_yield</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>div_yield_avg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pts_div_yield</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>indicator</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>forecast</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>surprise</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>signal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>spy_price</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>spy_day_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>qqq_day_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>buy_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>breadth_sma20</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>breadth_sma50</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>breadth_sma100</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>breadth_sma200</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>breadth_sma50_week_ago</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>advancers</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>decliners</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>universe_n</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>highs_52w</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lows_52w</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>put_call</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>put_call_ma5</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>put_call_zone</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>put_call_name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>vix</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>fred_dgs10</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fred_t10y2y</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>xly_xlp</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>updated_pt</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>price_as_of</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>macro_growth</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>macro_inflation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>macro_jobs</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>macro_score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>plain_english</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>desk_median_trailing_pe</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>official_sp500_pe</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>official_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dist_52w_high_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>volume_ratio</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>trend_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sma_alignment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rsi14</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>entry_low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>entry_high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>passes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>why</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>side</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>strike</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>open_interest</t>
+          <t>price</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>day_pct</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>is_wall</t>
+          <t>score</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>data_status</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>week_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>month_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>month3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ytd_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>score_avg</t>
+        </is>
+      </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ret_1d</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ret_1w</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ret_1m</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ret_ytd</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>above_sma20</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>above_sma50</t>
+        </is>
+      </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>above_sma100</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>above_sma200</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>disclaimer</t>
         </is>
       </c>
@@ -2834,13 +4425,100 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>field</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>n_missing</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>n_present</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>checked_pt</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,55 +4529,862 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>group_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>week_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>month_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>month3_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ytd_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rs_3m_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>score_avg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>n_stocks</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>macro_growth</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>macro_inflation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>macro_jobs</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>macro_score</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>topic</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plain_english</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>company</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>analyst_mean</t>
+          <t>sector</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>analyst_count</t>
+          <t>index_membership</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pts_analyst</t>
+          <t>in_sp500</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>target_analyst</t>
+          <t>in_ndx100</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>target_analyst_kind</t>
+          <t>in_growth</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>months</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>top20_cagr_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>spy_cagr_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>bottom20_cagr_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>top20_total_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>spy_total_pct</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>bottom20_total_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top20_max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spy_max_drawdown_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>hit_rate_12w_pct</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>top_bucket_excess_12w_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>is_headline</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>horizon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>bucket</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>bucket_order</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>avg_return_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>avg_spy_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>excess_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>hit_rate_pct</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>top20</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spy</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>bottom20</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>top20_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spy_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>difference_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>hit_rate_12w_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>signals</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pct_above_sma20</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pct_above_sma50</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pct_above_sma100</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pct_above_sma200</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score_prev</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>verdict_prev</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>price</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>upside_pct</t>
+          <t>data_status</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>score_prev</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>score_change</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>data_status</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>disclaimer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>company</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>avg_cost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>day_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cost</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gain</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gain_pct</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>weight_pct</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>score</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>score_week_ago</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>score_week_change</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>example</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>data_status</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>disclaimer</t>
         </is>
@@ -2908,2479 +5393,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>group_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>points</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>points_label</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>now_value</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>avg_value</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>vs_industry</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>row_type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>owner</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>increased_shares</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>decreased_shares</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>holders</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ownership_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>shares</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>share_change</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>as_of</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>pts_institutional</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>as_of</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>bullish_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>neutral_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bearish_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>buys_3m</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sells_3m</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pts_insider</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>headline</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>publisher</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>tone</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>tone_note</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>xly</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>xlp</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ratio_sma50</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>zone</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>now_value</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>avg_3y</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pts_vs_self</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>industry_median</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>pts_vs_industry</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>earnings_date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>eps_estimate</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>eps_actual</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>surprise_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>fy_end</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>filed</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>gross_profit</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>op_income</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>net_income</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>eps</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>gross_margin</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>operating_margin</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>net_margin</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>fcf</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>pe</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ps</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>pfcf</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>div_yield</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>div_yield_avg</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>dps</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pts_div_yield</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>indicator</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>forecast</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>surprise</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>signal</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>spy_price</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>spy_day_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>qqq_day_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>buy_count</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>breadth_sma20</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>breadth_sma50</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>breadth_sma100</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>breadth_sma200</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>breadth_sma50_week_ago</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>advancers</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>decliners</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>universe_n</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>highs_52w</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>lows_52w</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>put_call</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>put_call_ma5</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>put_call_zone</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>put_call_name</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>vix</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>fred_dgs10</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>fred_t10y2y</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>xly_xlp</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>updated_pt</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>price_as_of</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>macro_growth</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>macro_inflation</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>macro_jobs</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>macro_score</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>plain_english</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>desk_median_trailing_pe</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>official_sp500_pe</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>official_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>dist_52w_high_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>volume_ratio</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>trend_label</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>sma_alignment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>above_sma20</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>above_sma50</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>above_sma100</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>above_sma200</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>rsi14</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>entry_low</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>entry_high</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>passes</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>why</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>side</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>week_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>month_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>month3_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ytd_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>pct_above_sma50</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>score_avg</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ret_1d</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ret_1w</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>ret_1m</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ret_ytd</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>above_sma20</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>above_sma50</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>above_sma100</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>above_sma200</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>field</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>n_missing</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n_present</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>latest</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>checked_pt</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>group_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>week_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>month_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>month3_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ytd_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>rs_3m_pct</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>score_avg</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>n_stocks</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pct_above_sma50</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>macro_growth</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>macro_inflation</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>macro_jobs</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>macro_score</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>topic</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>plain_english</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>setting</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>index_membership</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>in_sp500</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>in_ndx100</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>in_growth</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>months</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>top20_cagr_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>spy_cagr_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bottom20_cagr_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>top20_total_pct</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>spy_total_pct</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>bottom20_total_pct</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>top20_max_drawdown_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>spy_max_drawdown_pct</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>hit_rate_12w_pct</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>top_bucket_excess_12w_pct</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>headline</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>is_headline</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>horizon</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>bucket</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>avg_return_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>avg_spy_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>excess_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>hit_rate_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>top20</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bottom20</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>top20_pct</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spy_pct</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>difference_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>hit_rate_12w_pct</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>signals</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pct_above_sma20</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>pct_above_sma50</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>pct_above_sma100</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>pct_above_sma200</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>kind</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>score_prev</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>verdict_prev</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>score_prev</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>score_change</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>company</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>shares</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>avg_cost</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>day_pct</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>cost</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>gain</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>gain_pct</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>weight_pct</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>score_week_ago</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>score_week_change</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>stop</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>example</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>data_status</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>disclaimer</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>